--- a/data/numeric/input/data_147/314班期中联考成绩.xlsx
+++ b/data/numeric/input/data_147/314班期中联考成绩.xlsx
@@ -2935,13 +2935,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3A775AF-287C-42D7-ABD6-4AF5CAE4EE58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{319A2829-2026-4926-9AE6-334D2F3A1971}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E463E2-86E0-4E6A-B27C-04E47AD70AAB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE06262A-4A04-4CAD-9A7D-DD5C0070C9D1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4808C993-3545-47CD-B149-F897D49F1F43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{597B9EC8-FD8D-4B2B-B330-4C85896A3B74}"/>
 </file>